--- a/AAII_Financials/Quarterly/CNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>CNI</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3346900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3137100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3255700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2990200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3132300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3063300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3028800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3042300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3163000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3137800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3385500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2947300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3063700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3187700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3343400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3288900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3210200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2695800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2778600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2660000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2602100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2654300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2828800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2613500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2518200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2783000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2794300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3175300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3139600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2728200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2898200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2680000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2733400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2377000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2444700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2397100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2477500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2462900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2471400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2315400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1522400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1432100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1376200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1272900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1341800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1397000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1353200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1376100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1433500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1451100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1454600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1301800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1333600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1428700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>918700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>851900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>908200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>772800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>683400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>631100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>656000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>685500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>671600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>577300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>584600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>736400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>773400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>781800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>803300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>735900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>755800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>670000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>688100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>650400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>634100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>547700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>566300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>600800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>568500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>491700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1824500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1705000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1879500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1717300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1790500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1666300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1675700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1666200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1729400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1686700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1930900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1645500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1730100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1759000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2424700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2437000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2302000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1922900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2095200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2028900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1946200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1968800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2157200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2036200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1933600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2046600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2020900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2393500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2336200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1992300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2142500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2010000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2045300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1726600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1810700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1849400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1911100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1862200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1902900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1823800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,43 +1496,46 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-47300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-16700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-13900</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>57000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-103000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1523,26 +1543,26 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-594100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1559,8 +1579,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>342200</v>
+      </c>
+      <c r="E15" s="3">
         <v>346700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>332600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>359000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>358500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>343000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>339900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>351600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>340500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>341200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>350600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>337800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>339100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>331100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>332000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>317000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>312600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>305300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>283600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>300000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>293600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>303300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>311000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>299800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>317000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>307700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>301700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>308400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>287900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>338700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>263300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>239800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>248400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>240400</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>235200</v>
       </c>
       <c r="AL15" s="3">
         <v>235200</v>
       </c>
       <c r="AM15" s="3">
+        <v>235200</v>
+      </c>
+      <c r="AN15" s="3">
         <v>242600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>248100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>238200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>239700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1999200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1932100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1875100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1747400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1838900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1856200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1818800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1836500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1884300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1912700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1918800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1736500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1764800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1871400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1936000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1880900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1902900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1803700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1619200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1010400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1602700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1657900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1737100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1566200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1902200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1829200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1844700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1838000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1805700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1896800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1793100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1595800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1589900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1610500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1710900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1311300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1424400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1522600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1399700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1234500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1347800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1205000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1380600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1242700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1293400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1207100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1210000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1205800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1278600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1225100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1466700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1210900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1298900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1316300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1407400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1408000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1307300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>892000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1159400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1649600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>999500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>996400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1091800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1047200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>616000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>953800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>949600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1337300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1333900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>831400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1105100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1084200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1143500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>766500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>733800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1085800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1053100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>940300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1071700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1080900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-23400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1500</v>
       </c>
       <c r="N20" s="3">
         <v>1500</v>
       </c>
       <c r="O20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>89800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>90400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>80700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>97000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>51100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>106300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>70600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>60400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>59800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>59600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>70700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>61600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>88700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>84100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>63100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>126300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>90100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>229600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>61800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>237400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>60300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>62200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>69900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1695000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1556700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1717600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1601000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1660000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1663700</v>
+      </c>
+      <c r="I21" s="3">
         <v>1550800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1534600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1564800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1642500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1567800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1815800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1547200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1638700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1648200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1829200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1815300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1704100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1278100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1539900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2000700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1399400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1370300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1463200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>992700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1332200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1313000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1734400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1705800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1233300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1494800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1414100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1621500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1068700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1206400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1324700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1356000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1250700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1379700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1320600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>169700</v>
+      </c>
+      <c r="E22" s="3">
         <v>167600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>178000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>160100</v>
       </c>
-      <c r="G22" s="3">
-        <v>156900</v>
-      </c>
       <c r="H22" s="3">
+        <v>160600</v>
+      </c>
+      <c r="I22" s="3">
         <v>162100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>160500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>170300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>160700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>155100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>150700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>136800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>130600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>122000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>112600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>102800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>94600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>91600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>92500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>145900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>114300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>97600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>103700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>105000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>113000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>109900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>106000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>111900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>107900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>100800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>92900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>87900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>90800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>87100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>88600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>91500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>93700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>94500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1183000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1089700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1217300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1081900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1144500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1062400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1048100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1043000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1084300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1071500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1417500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1072600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1169000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1195100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1384600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1395600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1296900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>881100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1163800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1554800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>991500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>969400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1048400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1002000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>562700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>914600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>905200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1314000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1310100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>793700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1138600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1086400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1279700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>737500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>884100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1001000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>908800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1047100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>990200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>303500</v>
+      </c>
+      <c r="E24" s="3">
         <v>268700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>307000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>264200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>285200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>254600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>251600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>239800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>270300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>257000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-195400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>253600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>287700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>293400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>339300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>335200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>317800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>213700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>276200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>306700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>243700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>238000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>258400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>246900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>135000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>231600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>224500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>323300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>230000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>188600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>268700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>262300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>186100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-2371800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>288000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>254500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>229700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>265000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>243500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E26" s="3">
         <v>821000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>910200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>817700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>859300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>807700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>796500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>803100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>813900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>814600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1612900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>819100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>881300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>901700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1045300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1060300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>979200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>667400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>887700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1248100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>747800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>731300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>790000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>755100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>427700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>683000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>680700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>990700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1080100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>605100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>869900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>824100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>986200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>551500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3255900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>713000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>767300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>679100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>782100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E27" s="3">
         <v>821000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>910200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>817700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>859300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>807700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>796500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>803100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>813900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>814600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1612900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>819100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>881300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>901700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1045300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1060300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>979200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>667400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>887700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1248100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>747800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>731300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>790000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>755100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>427700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>683000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>680700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>990700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1080100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>605100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>869900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>824100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>986200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>551500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3255900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>713000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>767300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>679100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>782100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3270,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -3218,8 +3279,8 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -3228,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>110700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1312800</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
-        <v>8100</v>
-      </c>
       <c r="H32" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>23400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1500</v>
       </c>
       <c r="N32" s="3">
         <v>-1500</v>
       </c>
       <c r="O32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-89800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-90400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-80700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-97000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-51100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-106300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-70600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-60400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-59800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-59600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-70700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-84100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-63100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-126300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-90100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-229600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-61800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-237400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-60300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-62200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-69900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E33" s="3">
         <v>821000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>910200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>817700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>859300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>807700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>796500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>803100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>813900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>814600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1612900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>819100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>881300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>901700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1045300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1060300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>979200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>667400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>887700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1248100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>747800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>731300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>790000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>755100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>427700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>793700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>680700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>990700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1080100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>605100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>869900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>824100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>986200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>551500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1943100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>713000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>767300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>679100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>782100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E35" s="3">
         <v>821000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>910200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>817700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>859300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>807700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>796500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>803100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>813900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>814600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1612900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>819100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>881300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>901700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1045300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1060300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>979200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>667400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>887700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1248100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>747800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>731300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>790000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>755100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>427700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>793700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>680700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>990700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1080100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>605100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>869900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>824100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>986200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>551500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1943100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>713000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>767300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>679100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>782100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,150 +4305,154 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E41" s="3">
         <v>410500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>255300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>153600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>158400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>161400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>270400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>202100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>244800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>304300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>359700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>363000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>407000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>357700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>241400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>293700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>343600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>356200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>620400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1625200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>411500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>388900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>440300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>218500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>294300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>383100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>49900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>213900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>101500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>261000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>202400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>230400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>296600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>180100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>52100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>81100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>97500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>203600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>135200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>165200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E42" s="3">
         <v>9300</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>8600</v>
-      </c>
-      <c r="G42" s="3">
-        <v>700</v>
       </c>
       <c r="H42" s="3">
         <v>700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -4463,507 +4553,522 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>924600</v>
+      </c>
+      <c r="E43" s="3">
         <v>896900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>814700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>894500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>829300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>874500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>908400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>920100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>893600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>969600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>984400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>949200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>923600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1023600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1043100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1112100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1003500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>967700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>795100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>902200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>901900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>928100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>815500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1135400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1104900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1287500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>945700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1029700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1011100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>961500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>889700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>819000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>811500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>773200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>732300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>724100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>669000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>693700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>672200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>606300</v>
+      </c>
+      <c r="E44" s="3">
         <v>595300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>535300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>560000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>599000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>562800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>500400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>536700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>575700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>578200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>529300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>562600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>571700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>564700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>509400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>514500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>540200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>479800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>436100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>460700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>461400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>475300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>451100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>472300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>509300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>533000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>476400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>504100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>517000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>505000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>423900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>409100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>420100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>387700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>315500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>314100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>337100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>316500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>272700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E45" s="3">
         <v>262200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>178000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>203800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>253900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>54200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>279100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>244800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>239300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>283900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>223500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>243900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>574200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>549500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>591200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>551100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>684800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>668900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>746400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>741100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>693300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>593400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>636400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>635100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>734400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>789300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>641600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>603500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>560200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>547900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>611300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>654200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>529900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>460700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>501600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>560000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>538500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>527000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2004800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2183600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1802200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1803400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2102100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1861800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1820200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2252500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2286900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2423000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2339000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2492000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2466400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2524700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2368100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2469800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2478600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2354800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2536500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3657000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2521100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2533400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2400200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2419500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2544900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2838700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2206500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2536900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2271200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2331000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2076300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2006400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2139400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1995200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1629800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1580000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1605300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1773800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1618700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1666300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>81000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4971,11 +5076,11 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>297500</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -4983,11 +5088,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>304400</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,175 +5178,181 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35551700</v>
+      </c>
+      <c r="E48" s="3">
         <v>35699900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34940800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35271300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35214000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34023000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32510200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34469100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33668200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33653600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32933500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33233800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33198900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32477200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32394000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32016600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31178000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30088800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30816000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30516300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>29155200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30198800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>31340000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31349400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32130400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32890500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31334200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>33081600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31003900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>29735800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>28748700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26073600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26708200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>25820400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>25443800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>24901300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>25047100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>25878600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>25931600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>25320100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>381700</v>
+      </c>
+      <c r="E49" s="3">
         <v>350300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1385700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>359000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>354900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>341600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1297600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>552200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>541400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>546500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1324400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>303800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>304300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>300100</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5260,50 +5371,50 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-      <c r="X49" s="3" t="s">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>325700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>317400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>328000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>341500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>334500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>289300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>276000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>271700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>203200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>191800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>201700</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>190500</v>
-      </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3950400</v>
+      </c>
+      <c r="E52" s="3">
         <v>3930200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3950800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3504900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3496700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3239300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3175500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2566300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2453500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2397900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2398900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2476400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2450500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2320000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2530700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2830500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2764600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2624500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2583100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1205900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1777000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1029400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>601200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>533600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>466100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>383100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>262000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>650000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>550400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>462700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>339400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>947600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>915400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1028500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>739700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1131900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1065700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1025600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>918000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1490400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42316700</v>
+      </c>
+      <c r="E54" s="3">
         <v>42599500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42706000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41391600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41628900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39936700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39661800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40327900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39446200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39526800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39879500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38506000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38420200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37622000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37292800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37316900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36421100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35068100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35935600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35379200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33453300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33761700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34667100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34619900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35469500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36453800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34137100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36557800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34101400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32801300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31367600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>29219500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29964800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28844100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28003900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>27613200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27718100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>28678000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>28468300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>28476700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,287 +6145,294 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1868200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1935000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>649100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1774000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1640200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1662100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>716500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1856500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1748400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1731000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>733000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1655900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1721000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1691800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1815200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1869300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1706300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1704100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1659100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1559300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1387900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1467200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1636500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1443600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1643200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1552800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1539800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1596800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1639200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1616600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1762700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1440300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1483000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1343300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1402100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1286000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1265900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1259100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1166200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1234500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>433800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1331800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>739500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1221900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>932600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1335800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>903500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1632200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1852200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2311500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1860500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1786000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>922800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1718400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>778100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>577200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1808300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1093400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>376100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>906700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1142000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>507600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>704100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>667700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>827900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2034800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1504800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1808200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1460700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>901100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1324800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1850400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1901500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1548000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1282300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1350700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1200700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1143900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>515500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>574000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>389900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>456600</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
@@ -6303,11 +6440,11 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>234800</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
@@ -6315,440 +6452,452 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V59" s="3">
         <v>274700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>165200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>182300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>156200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>192700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>185500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>161700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>297800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>166600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>172900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>134700</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
-      </c>
       <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
         <v>10200</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>1500</v>
       </c>
       <c r="AJ59" s="3">
         <v>1500</v>
       </c>
       <c r="AK59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AL59" s="3">
         <v>14100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>23800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2302000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3266800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2695600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2995900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2572800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2998600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2763300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3493100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3602100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4042500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3812600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3441900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2643900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3410200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2828100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2446400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3514600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2797500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2309900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2631100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2712100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2130900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2533300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2296900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2632800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3719600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3342400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3571500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3272800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3091600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2663800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2775200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3334900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3246200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2964200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2586900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2640500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2462900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2310800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1760800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15588300</v>
+      </c>
+      <c r="E61" s="3">
         <v>14906200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15035900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14301200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14417200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13453900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13949400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13957600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13405900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12567600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12441800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12119800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12177900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10822500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10579400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10639900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8812500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8636200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8867300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9134800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8779900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9199500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9281900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9901200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10285600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9966200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9251600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9606200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9129200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9000700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8665000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7318500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7088300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6963600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6510300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6467900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6505900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7191400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7258200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7699200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>618300</v>
+      </c>
+      <c r="E62" s="3">
         <v>631900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>349300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>558600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>528600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>466100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>296100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>416700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>382900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>370700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>333200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>334900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>348100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>328900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8144300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8197800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8025400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7747700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7919600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7568900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7252500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7495800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7647000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7615800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7817600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7982400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7477000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8042600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7439300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7215500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6612300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6331600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6466500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6289300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6133800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7332000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7370700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7590900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7497900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>7405700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26894600</v>
+      </c>
+      <c r="E66" s="3">
         <v>27232000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26975800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26119100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25838400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24892300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25031300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25924700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25268700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24864900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24646600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23742700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23016200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22205300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21551800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21284200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20352500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19181400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19096800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19334800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18744400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18826300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19462100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19813800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20736000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21668200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20071000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21220400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19841400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19307900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17941200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16425400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16889600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16499100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15608300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>16386800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>16517000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17245200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17067000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>16865700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13339900</v>
+      </c>
+      <c r="E72" s="3">
         <v>13388900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13797500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13489200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14077700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13135300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12756100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13240300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12968300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13481100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14125800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13392000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14104400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14070100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14375500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14306300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14644600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14644200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15355800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15557000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14374700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14565900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14825800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14220400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14106500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14005300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13748700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14554000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13582100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12765200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12651600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11850100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12046900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>11455600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11599300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>10207600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10101200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>10254300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>10172900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9933200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15422200</v>
+      </c>
+      <c r="E76" s="3">
         <v>15367600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15730200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15272600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15790500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15044400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14630500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14403200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14177500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14661900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15232900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14763300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15404000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15416700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15741000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16032700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16068600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15886600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16838700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16044400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14708800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14935400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15205000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14806100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14733500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14785600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14066000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15337400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14260100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13493400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13426400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12794100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13075200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12345000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12395600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11226400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11201100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11432800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11401300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>11611000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E81" s="3">
         <v>821000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>910200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>817700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>859300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>807700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>796500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>803100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>813900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>814600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1612900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>819100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>881300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>901700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1045300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1060300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>979200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>667400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>887700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1248100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>747800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>731300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>790000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>755100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>427700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>793700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>680700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>990700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1080100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>605100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>869900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>824100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>986200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>551500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1943100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>713000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>767300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>679100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>782100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>358500</v>
+      </c>
+      <c r="E83" s="3">
         <v>343000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>339900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>351600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>340500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>341200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>350600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>337800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>339100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>331100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>333200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>316800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>328400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>336400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>332000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>317000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>312600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>305300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>283600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>300000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>293600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>303300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>311000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>299800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>317000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>307700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>301700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>308400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>287900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>338700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>263300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>239800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>248400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>240400</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>235200</v>
       </c>
       <c r="AL83" s="3">
         <v>235200</v>
       </c>
       <c r="AM83" s="3">
+        <v>235200</v>
+      </c>
+      <c r="AN83" s="3">
         <v>242600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>248100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>238200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>239700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1134400</v>
+      </c>
+      <c r="E89" s="3">
         <v>906300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1624200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1373400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1279500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>809800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1386500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1313200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1324700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>824900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1827200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1117700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1499000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>779700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1672400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1539100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1265900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>414400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1544400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1820700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1066700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>714800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1553700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>935300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1378800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>926400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1183500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1402800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1360800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>767500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1459000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1136500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1266200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>561900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1003900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1046400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1120000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>964900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1058600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1143100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-489400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-314500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-896300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-793300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-590200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-361100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-656100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-870500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-623200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-425400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-707200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-677900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-660800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-340700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-920000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-744000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-707000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-379000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-914000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-836000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-527200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-309400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-661600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-529700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-560300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-473400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-793700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-796700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-938100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-541200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-962000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-728100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-632300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-316300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-653400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-538800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-502300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-304200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1023300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1367400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-471100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-261500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-898500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-804100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-603400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-374300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-669300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-880900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-632700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-434200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-901100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-688200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-668300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-341500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-689700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-550900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-529100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-73400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-636700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>31100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1187500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-310100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-671600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-553500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-587800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-476500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-870900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-822400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-675900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-977200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-711400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-533000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-322200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-663800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-553700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-516500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-313400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-458600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-694500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>390100</v>
+      </c>
+      <c r="E96" s="3">
         <v>399800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>397500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>394900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>407700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>387500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>369000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>393800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>390900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>398800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>385400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>380700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>393400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>388800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-362900</v>
       </c>
       <c r="R96" s="3">
         <v>-362900</v>
       </c>
       <c r="S96" s="3">
+        <v>-362900</v>
+      </c>
+      <c r="T96" s="3">
         <v>-372500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-370000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-320600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-322200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-315300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-327400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-316500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-312800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-320200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-321100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-298600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-319200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-306900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-299500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-251900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-241300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-251400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-250100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-228500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-230000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-230700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-240500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-220500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-221300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,217 +10953,223 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-870400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-485700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-625000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-868000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-382700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-544800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-926400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-495200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-748900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-437900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-938900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-466500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-789200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-362200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1035000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1073500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-756000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-556200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1904200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-672600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>155500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-444500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-661600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-449300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-875000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-118500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-463900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-438600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-519800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-468000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-618800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-118300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-369900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-496400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-697300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-610000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-635300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-407200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>700</v>
       </c>
       <c r="H101" s="3">
         <v>700</v>
       </c>
       <c r="I101" s="3">
+        <v>700</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2200</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-800</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2400</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-800</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -10928,152 +11177,158 @@
         <v>0</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>5400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-205600</v>
+      </c>
+      <c r="E102" s="3">
         <v>159000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>99900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-297200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>290400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-109200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-206400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-63700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-56300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-46500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-35500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>76100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-53000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-83100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-215200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-996500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1180000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>34000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>219700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-67500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-85500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>333600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-151300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>140900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-164200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>46200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-38100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-50900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>115900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>128000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-28300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-98200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>39900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>42300</v>
       </c>
     </row>
